--- a/LLM_Extraction_and_CrossCritique/interactive-table/results/pipeline_comparison_p1_vs_p4.xlsx
+++ b/LLM_Extraction_and_CrossCritique/interactive-table/results/pipeline_comparison_p1_vs_p4.xlsx
@@ -1,36 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhrub\Mayo-CoRAL\LLM_Extraction_and_CrossCritique\interactive-table\results\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9135A694-2D2D-4890-A8F1-6FAFF96DE600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="query_by_query" sheetId="1" r:id="rId1"/>
     <sheet name="summary" sheetId="2" r:id="rId2"/>
     <sheet name="color_counts" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -418,8 +399,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -480,11 +461,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -498,48 +479,19 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -577,7 +529,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -611,7 +563,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -646,10 +597,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -822,11 +772,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J102"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -858,7 +808,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10">
       <c r="A2">
         <v>0</v>
       </c>
@@ -866,16 +816,16 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E2">
-        <v>0.66666666666666663</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F2">
-        <v>0.74074074074074081</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -884,13 +834,13 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>0.83333333333333337</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="J2">
-        <v>0.55555555555555558</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3">
         <v>1</v>
       </c>
@@ -898,16 +848,16 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F3">
-        <v>0.66666666666666663</v>
+        <v>0.7407407407407408</v>
       </c>
       <c r="G3">
         <v>0.5</v>
@@ -916,13 +866,13 @@
         <v>0.5</v>
       </c>
       <c r="I3">
-        <v>0.66666666666666663</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="J3">
-        <v>0.44444444444444442</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.5925925925925926</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4">
         <v>2</v>
       </c>
@@ -936,10 +886,10 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0.5</v>
+        <v>0.7925925925925926</v>
       </c>
       <c r="F4">
-        <v>0.55555555555555558</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -948,13 +898,13 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J4">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5">
         <v>3</v>
       </c>
@@ -962,31 +912,31 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D5">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E5">
-        <v>0.40000000000000008</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="F5">
-        <v>0.44444444444444442</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="G5">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0.80000000000000016</v>
+        <v>0.4719576719576719</v>
       </c>
       <c r="J5">
-        <v>0.44444444444444442</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.4444444444444444</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6">
         <v>4</v>
       </c>
@@ -994,13 +944,13 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>0.40000000000000008</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="F6">
         <v>0.5714285714285714</v>
@@ -1012,13 +962,13 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>0.5714285714285714</v>
+        <v>0.5</v>
       </c>
       <c r="J6">
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1032,25 +982,25 @@
         <v>0.5</v>
       </c>
       <c r="E7">
-        <v>0.69999999999999984</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F7">
-        <v>0.77777777777777779</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G7">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H7">
         <v>0.5</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="J7">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7777777777777778</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1064,10 +1014,10 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>0.40000000000000008</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="F8">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1076,13 +1026,13 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>0.46296296296296302</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="J8">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1102,10 +1052,10 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -1114,7 +1064,7 @@
         <v>0.8571428571428571</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1122,31 +1072,31 @@
         <v>18</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>0.43333333333333329</v>
+        <v>0.6</v>
       </c>
       <c r="F10">
-        <v>0.61904761904761907</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0.83333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="J10">
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1163,7 +1113,7 @@
         <v>0.5</v>
       </c>
       <c r="F11">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1175,10 +1125,10 @@
         <v>1</v>
       </c>
       <c r="J11">
-        <v>0.72222222222222221</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1192,7 +1142,7 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>0.69999999999999984</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F12">
         <v>0.875</v>
@@ -1204,13 +1154,13 @@
         <v>1</v>
       </c>
       <c r="I12">
-        <v>0.66666666666666663</v>
+        <v>0.8101851851851851</v>
       </c>
       <c r="J12">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1224,7 +1174,7 @@
         <v>1</v>
       </c>
       <c r="E13">
-        <v>0.69999999999999984</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F13">
         <v>0.875</v>
@@ -1236,13 +1186,13 @@
         <v>0.5</v>
       </c>
       <c r="I13">
-        <v>0.5</v>
+        <v>0.5047619047619047</v>
       </c>
       <c r="J13">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.5416666666666666</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1256,25 +1206,25 @@
         <v>1</v>
       </c>
       <c r="E14">
-        <v>0.69999999999999984</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F14">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>0.7259259259259259</v>
+      </c>
+      <c r="J14">
         <v>0.875</v>
       </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J14">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1288,10 +1238,10 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F15">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G15">
         <v>0.5</v>
@@ -1300,13 +1250,13 @@
         <v>0.5</v>
       </c>
       <c r="I15">
-        <v>0.54761904761904756</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="J15">
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1314,31 +1264,31 @@
         <v>24</v>
       </c>
       <c r="C16">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
-        <v>0.5</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F16">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G16">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H16">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>0.4296296296296296</v>
       </c>
       <c r="J16">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1346,16 +1296,16 @@
         <v>25</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E17">
-        <v>0.40000000000000008</v>
+        <v>0.5</v>
       </c>
       <c r="F17">
-        <v>0.66666666666666663</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1364,13 +1314,13 @@
         <v>1</v>
       </c>
       <c r="I17">
-        <v>0.71111111111111114</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="J17">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1384,10 +1334,10 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>0.69999999999999984</v>
+        <v>0.6</v>
       </c>
       <c r="F18">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1396,13 +1346,13 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>0.66666666666666663</v>
+        <v>0.6148148148148148</v>
       </c>
       <c r="J18">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.5833333333333334</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1410,31 +1360,31 @@
         <v>27</v>
       </c>
       <c r="C19">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E19">
-        <v>0.46666666666666662</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F19">
-        <v>0.58333333333333337</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H19">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="I19">
-        <v>0.625</v>
+        <v>0.5</v>
       </c>
       <c r="J19">
         <v>0.625</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1442,16 +1392,16 @@
         <v>28</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E20">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F20">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1460,13 +1410,13 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>0.80000000000000016</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="J20">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.5833333333333334</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1480,25 +1430,25 @@
         <v>1</v>
       </c>
       <c r="E21">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F21">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H21">
         <v>1</v>
       </c>
       <c r="I21">
-        <v>0.5714285714285714</v>
+        <v>0.875</v>
       </c>
       <c r="J21">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1506,31 +1456,31 @@
         <v>30</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D22">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E22">
-        <v>0.5</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F22">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H22">
         <v>0.75</v>
       </c>
       <c r="I22">
-        <v>0.5714285714285714</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="J22">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7916666666666666</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1538,16 +1488,16 @@
         <v>31</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E23">
-        <v>0.66666666666666663</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F23">
-        <v>0.83333333333333337</v>
+        <v>0.875</v>
       </c>
       <c r="G23">
         <v>0.75</v>
@@ -1556,13 +1506,13 @@
         <v>0.75</v>
       </c>
       <c r="I23">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1588,13 +1538,13 @@
         <v>1</v>
       </c>
       <c r="I24">
-        <v>0.66666666666666663</v>
+        <v>0.8412698412698413</v>
       </c>
       <c r="J24">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1602,31 +1552,31 @@
         <v>33</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F25">
-        <v>0.75</v>
+        <v>0.625</v>
       </c>
       <c r="G25">
-        <v>0.66666666666666663</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I25">
-        <v>0.75555555555555554</v>
+        <v>0.769047619047619</v>
       </c>
       <c r="J25">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7916666666666666</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1634,31 +1584,31 @@
         <v>34</v>
       </c>
       <c r="C26">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
-        <v>0.40000000000000008</v>
+        <v>0.6</v>
       </c>
       <c r="F26">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H26">
         <v>1</v>
       </c>
       <c r="I26">
-        <v>0.80000000000000016</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="J26">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7083333333333334</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1666,16 +1616,16 @@
         <v>35</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27">
-        <v>0.5</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F27">
-        <v>0.625</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -1684,13 +1634,13 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0.5714285714285714</v>
+        <v>0.6296296296296297</v>
       </c>
       <c r="J27">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7083333333333334</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1710,19 +1660,19 @@
         <v>0.625</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28">
-        <v>0.5</v>
+        <v>0.525925925925926</v>
       </c>
       <c r="J28">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1736,10 +1686,10 @@
         <v>1</v>
       </c>
       <c r="E29">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F29">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -1748,13 +1698,13 @@
         <v>1</v>
       </c>
       <c r="I29">
-        <v>0.5714285714285714</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J29">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1762,16 +1712,16 @@
         <v>38</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
-        <v>0.6</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F30">
-        <v>0.75</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -1780,13 +1730,13 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>0.72222222222222221</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="J30">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7083333333333334</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1800,10 +1750,10 @@
         <v>1</v>
       </c>
       <c r="E31">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F31">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -1812,13 +1762,13 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>0.58333333333333337</v>
+        <v>0.6</v>
       </c>
       <c r="J31">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1826,7 +1776,7 @@
         <v>40</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -1844,13 +1794,13 @@
         <v>1</v>
       </c>
       <c r="I32">
-        <v>0.80000000000000016</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="J32">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1876,13 +1826,13 @@
         <v>1</v>
       </c>
       <c r="I33">
-        <v>0.66666666666666663</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="J33">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7916666666666666</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1890,16 +1840,16 @@
         <v>42</v>
       </c>
       <c r="C34">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E34">
-        <v>0.43333333333333329</v>
+        <v>0.6</v>
       </c>
       <c r="F34">
-        <v>0.54166666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -1908,13 +1858,13 @@
         <v>1</v>
       </c>
       <c r="I34">
-        <v>0.60317460317460314</v>
+        <v>0.5462962962962963</v>
       </c>
       <c r="J34">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.5833333333333334</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1928,10 +1878,10 @@
         <v>1</v>
       </c>
       <c r="E35">
-        <v>0.46666666666666662</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F35">
-        <v>0.58333333333333337</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -1940,13 +1890,13 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <v>0.5</v>
+        <v>0.6944444444444443</v>
       </c>
       <c r="J35">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1954,31 +1904,31 @@
         <v>44</v>
       </c>
       <c r="C36">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D36">
-        <v>0.5</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E36">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F36">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G36">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I36">
-        <v>0.63492063492063489</v>
+        <v>0.75</v>
       </c>
       <c r="J36">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1992,10 +1942,10 @@
         <v>1</v>
       </c>
       <c r="E37">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F37">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2004,13 +1954,13 @@
         <v>1</v>
       </c>
       <c r="I37">
-        <v>0.56084656084656082</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="J37">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38">
         <v>36</v>
       </c>
@@ -2024,10 +1974,10 @@
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0.40000000000000008</v>
+        <v>0.5</v>
       </c>
       <c r="F38">
-        <v>0.5</v>
+        <v>0.625</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -2036,13 +1986,13 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>0.66666666666666663</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="J38">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39">
         <v>37</v>
       </c>
@@ -2056,25 +2006,25 @@
         <v>1</v>
       </c>
       <c r="E39">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F39">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G39">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
       <c r="I39">
-        <v>0.50462962962962965</v>
+        <v>0.7518518518518519</v>
       </c>
       <c r="J39">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40">
         <v>38</v>
       </c>
@@ -2100,13 +2050,13 @@
         <v>1</v>
       </c>
       <c r="I40">
-        <v>0.5714285714285714</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="J40">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41">
         <v>39</v>
       </c>
@@ -2114,7 +2064,7 @@
         <v>49</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -2123,22 +2073,22 @@
         <v>0.6333333333333333</v>
       </c>
       <c r="F41">
-        <v>0.79166666666666663</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H41">
         <v>1</v>
       </c>
       <c r="I41">
-        <v>0.5714285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="J41">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42">
         <v>40</v>
       </c>
@@ -2164,13 +2114,13 @@
         <v>1</v>
       </c>
       <c r="I42">
-        <v>0.66666666666666663</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="J42">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43">
         <v>41</v>
       </c>
@@ -2184,10 +2134,10 @@
         <v>1</v>
       </c>
       <c r="E43">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F43">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2196,13 +2146,13 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <v>0.66666666666666663</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="J43">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44">
         <v>42</v>
       </c>
@@ -2216,10 +2166,10 @@
         <v>1</v>
       </c>
       <c r="E44">
-        <v>0.6333333333333333</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F44">
-        <v>0.79166666666666663</v>
+        <v>0.875</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -2228,13 +2178,13 @@
         <v>1</v>
       </c>
       <c r="I44">
-        <v>0.66666666666666663</v>
+        <v>0.8842592592592592</v>
       </c>
       <c r="J44">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7916666666666666</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45">
         <v>43</v>
       </c>
@@ -2248,10 +2198,10 @@
         <v>1</v>
       </c>
       <c r="E45">
-        <v>0.40000000000000008</v>
+        <v>0.6</v>
       </c>
       <c r="F45">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2260,13 +2210,13 @@
         <v>1</v>
       </c>
       <c r="I45">
-        <v>0.54761904761904756</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="J45">
         <v>0.5</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10">
       <c r="A46">
         <v>44</v>
       </c>
@@ -2274,31 +2224,31 @@
         <v>54</v>
       </c>
       <c r="C46">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E46">
-        <v>0.56666666666666665</v>
+        <v>0.6</v>
       </c>
       <c r="F46">
-        <v>0.70833333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="H46">
         <v>1</v>
       </c>
       <c r="I46">
-        <v>0.80000000000000016</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="J46">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7083333333333334</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47">
         <v>45</v>
       </c>
@@ -2306,31 +2256,31 @@
         <v>55</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E47">
-        <v>0.40000000000000008</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F47">
-        <v>0.5</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47">
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="J47">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48">
         <v>46</v>
       </c>
@@ -2338,31 +2288,31 @@
         <v>56</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>0.40000000000000008</v>
+        <v>0.6</v>
       </c>
       <c r="F48">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G48">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>0.61111111111111105</v>
+        <v>0.5</v>
       </c>
       <c r="J48">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49">
         <v>47</v>
       </c>
@@ -2370,16 +2320,16 @@
         <v>57</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49">
-        <v>0.53333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F49">
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -2388,13 +2338,13 @@
         <v>1</v>
       </c>
       <c r="I49">
-        <v>0.5714285714285714</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J49">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="A50">
         <v>48</v>
       </c>
@@ -2402,31 +2352,31 @@
         <v>58</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>0.53333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F50">
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50">
-        <v>0.60317460317460314</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J50">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="A51">
         <v>49</v>
       </c>
@@ -2440,10 +2390,10 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0.56666666666666665</v>
+        <v>0.6</v>
       </c>
       <c r="F51">
-        <v>0.70833333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2452,13 +2402,13 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>0.61111111111111105</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="J51">
         <v>0.5</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10">
       <c r="A52">
         <v>50</v>
       </c>
@@ -2466,10 +2416,10 @@
         <v>60</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E52">
         <v>0.6</v>
@@ -2478,19 +2428,19 @@
         <v>0.75</v>
       </c>
       <c r="G52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52">
-        <v>0.66666666666666663</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J52">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
       <c r="A53">
         <v>51</v>
       </c>
@@ -2504,10 +2454,10 @@
         <v>1</v>
       </c>
       <c r="E53">
-        <v>0.46666666666666662</v>
+        <v>0.5</v>
       </c>
       <c r="F53">
-        <v>0.58333333333333337</v>
+        <v>0.625</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -2516,13 +2466,13 @@
         <v>1</v>
       </c>
       <c r="I53">
-        <v>0.77777777777777779</v>
+        <v>0.7259259259259259</v>
       </c>
       <c r="J53">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
       <c r="A54">
         <v>52</v>
       </c>
@@ -2533,13 +2483,13 @@
         <v>1</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E54">
-        <v>0.53333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F54">
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -2548,13 +2498,13 @@
         <v>0.5</v>
       </c>
       <c r="I54">
-        <v>0.83333333333333337</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="J54">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7083333333333334</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
       <c r="A55">
         <v>53</v>
       </c>
@@ -2565,28 +2515,28 @@
         <v>1</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E55">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F55">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G55">
-        <v>0.44444444444444442</v>
+        <v>0.5</v>
       </c>
       <c r="H55">
         <v>0.5</v>
       </c>
       <c r="I55">
-        <v>0.63492063492063489</v>
+        <v>0.6</v>
       </c>
       <c r="J55">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
       <c r="A56">
         <v>54</v>
       </c>
@@ -2597,7 +2547,7 @@
         <v>1</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E56">
         <v>0.6</v>
@@ -2606,19 +2556,19 @@
         <v>0.75</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H56">
         <v>0.5</v>
       </c>
       <c r="I56">
-        <v>0.7142857142857143</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="J56">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
       <c r="A57">
         <v>55</v>
       </c>
@@ -2644,13 +2594,13 @@
         <v>0.5</v>
       </c>
       <c r="I57">
-        <v>0.52380952380952384</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="J57">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
       <c r="A58">
         <v>56</v>
       </c>
@@ -2664,10 +2614,10 @@
         <v>1</v>
       </c>
       <c r="E58">
-        <v>0.61111111111111116</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F58">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -2676,13 +2626,13 @@
         <v>1</v>
       </c>
       <c r="I58">
-        <v>0.80000000000000016</v>
+        <v>0.8042328042328042</v>
       </c>
       <c r="J58">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
       <c r="A59">
         <v>57</v>
       </c>
@@ -2696,25 +2646,25 @@
         <v>1</v>
       </c>
       <c r="E59">
-        <v>0.5</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="F59">
-        <v>0.625</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59">
-        <v>0.77777777777777779</v>
+        <v>0.6455026455026455</v>
       </c>
       <c r="J59">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
       <c r="A60">
         <v>58</v>
       </c>
@@ -2722,10 +2672,10 @@
         <v>68</v>
       </c>
       <c r="C60">
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="D60">
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="E60">
         <v>0.5</v>
@@ -2740,13 +2690,13 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>0.69444444444444431</v>
+        <v>0.5703703703703704</v>
       </c>
       <c r="J60">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7619047619047619</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
       <c r="A61">
         <v>59</v>
       </c>
@@ -2760,25 +2710,25 @@
         <v>1</v>
       </c>
       <c r="E61">
-        <v>0.5</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F61">
-        <v>0.7142857142857143</v>
+        <v>0.8095238095238094</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="H61">
         <v>1</v>
       </c>
       <c r="I61">
-        <v>0.79365079365079361</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="J61">
-        <v>0.7142857142857143</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
       <c r="A62">
         <v>60</v>
       </c>
@@ -2792,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0.40000000000000008</v>
+        <v>0.5</v>
       </c>
       <c r="F62">
-        <v>0.44444444444444442</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -2804,13 +2754,13 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>0.5714285714285714</v>
+        <v>0.7936507936507936</v>
       </c>
       <c r="J62">
-        <v>0.44444444444444442</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.5555555555555556</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
       <c r="A63">
         <v>61</v>
       </c>
@@ -2818,16 +2768,16 @@
         <v>71</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63">
-        <v>0.40000000000000008</v>
+        <v>0.6</v>
       </c>
       <c r="F63">
-        <v>0.5714285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -2836,13 +2786,13 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>0.88888888888888895</v>
+        <v>0.6203703703703703</v>
       </c>
       <c r="J63">
-        <v>0.7142857142857143</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7619047619047619</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
       <c r="A64">
         <v>62</v>
       </c>
@@ -2856,10 +2806,10 @@
         <v>1</v>
       </c>
       <c r="E64">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F64">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -2874,7 +2824,7 @@
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10">
       <c r="A65">
         <v>63</v>
       </c>
@@ -2882,31 +2832,31 @@
         <v>73</v>
       </c>
       <c r="C65">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D65">
         <v>1</v>
       </c>
       <c r="E65">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F65">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65">
         <v>1</v>
       </c>
       <c r="I65">
-        <v>0.72222222222222232</v>
+        <v>0.5851851851851851</v>
       </c>
       <c r="J65">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7083333333333334</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
       <c r="A66">
         <v>64</v>
       </c>
@@ -2914,16 +2864,16 @@
         <v>74</v>
       </c>
       <c r="C66">
-        <v>0.44444444444444442</v>
+        <v>0.5</v>
       </c>
       <c r="D66">
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="E66">
-        <v>0.56666666666666665</v>
+        <v>0.6</v>
       </c>
       <c r="F66">
-        <v>0.70833333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="G66">
         <v>0.5</v>
@@ -2932,13 +2882,13 @@
         <v>0.5</v>
       </c>
       <c r="I66">
-        <v>0.52380952380952384</v>
+        <v>0.75</v>
       </c>
       <c r="J66">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
       <c r="A67">
         <v>65</v>
       </c>
@@ -2946,31 +2896,31 @@
         <v>75</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E67">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F67">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G67">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H67">
         <v>0.5</v>
       </c>
       <c r="I67">
-        <v>0.5714285714285714</v>
+        <v>0.7797619047619048</v>
       </c>
       <c r="J67">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7083333333333334</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
       <c r="A68">
         <v>66</v>
       </c>
@@ -2984,25 +2934,25 @@
         <v>0.5</v>
       </c>
       <c r="E68">
-        <v>0.40000000000000008</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="F68">
-        <v>0.5714285714285714</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>0.3888888888888888</v>
       </c>
       <c r="H68">
         <v>0.5</v>
       </c>
       <c r="I68">
-        <v>0.80000000000000016</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="J68">
-        <v>0.5714285714285714</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
       <c r="A69">
         <v>67</v>
       </c>
@@ -3010,31 +2960,31 @@
         <v>77</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="D69">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E69">
         <v>0.5</v>
       </c>
       <c r="F69">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G69">
-        <v>0.66666666666666663</v>
+        <v>0.6</v>
       </c>
       <c r="H69">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="I69">
-        <v>1</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="J69">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
       <c r="A70">
         <v>68</v>
       </c>
@@ -3042,31 +2992,31 @@
         <v>78</v>
       </c>
       <c r="C70">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="D70">
-        <v>0.33333333333333331</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="E70">
         <v>0.5</v>
       </c>
       <c r="F70">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G70">
-        <v>0.33333333333333331</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="H70">
-        <v>0.33333333333333331</v>
+        <v>0.5555555555555555</v>
       </c>
       <c r="I70">
-        <v>1</v>
+        <v>0.6654761904761904</v>
       </c>
       <c r="J70">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7222222222222222</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
       <c r="A71">
         <v>69</v>
       </c>
@@ -3080,25 +3030,25 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F71">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0.5</v>
+      </c>
+      <c r="J71">
         <v>0.7142857142857143</v>
       </c>
-      <c r="G71">
-        <v>0</v>
-      </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>0.60317460317460314</v>
-      </c>
-      <c r="J71">
-        <v>0.5714285714285714</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:10">
       <c r="A72">
         <v>70</v>
       </c>
@@ -3106,16 +3056,16 @@
         <v>80</v>
       </c>
       <c r="C72">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="D72">
-        <v>0.66666666666666663</v>
+        <v>1</v>
       </c>
       <c r="E72">
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="F72">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -3124,13 +3074,13 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>0.65476190476190477</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="J72">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
       <c r="A73">
         <v>71</v>
       </c>
@@ -3144,10 +3094,10 @@
         <v>1</v>
       </c>
       <c r="E73">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F73">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -3156,13 +3106,13 @@
         <v>1</v>
       </c>
       <c r="I73">
-        <v>0.60317460317460314</v>
+        <v>0.6</v>
       </c>
       <c r="J73">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
       <c r="A74">
         <v>72</v>
       </c>
@@ -3176,10 +3126,10 @@
         <v>1</v>
       </c>
       <c r="E74">
-        <v>0.56666666666666665</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F74">
-        <v>0.70833333333333337</v>
+        <v>0.875</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -3188,13 +3138,13 @@
         <v>1</v>
       </c>
       <c r="I74">
-        <v>0.75555555555555554</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="J74">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7916666666666666</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
       <c r="A75">
         <v>73</v>
       </c>
@@ -3208,25 +3158,25 @@
         <v>1</v>
       </c>
       <c r="E75">
-        <v>0.40000000000000008</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="F75">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75">
+        <v>0.4814814814814815</v>
+      </c>
+      <c r="J75">
         <v>0.5714285714285714</v>
       </c>
-      <c r="G75">
-        <v>1</v>
-      </c>
-      <c r="H75">
-        <v>1</v>
-      </c>
-      <c r="I75">
-        <v>0.625</v>
-      </c>
-      <c r="J75">
-        <v>0.7142857142857143</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:10">
       <c r="A76">
         <v>74</v>
       </c>
@@ -3240,10 +3190,10 @@
         <v>1</v>
       </c>
       <c r="E76">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F76">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -3252,13 +3202,13 @@
         <v>1</v>
       </c>
       <c r="I76">
-        <v>0.57870370370370372</v>
+        <v>0.6</v>
       </c>
       <c r="J76">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
       <c r="A77">
         <v>75</v>
       </c>
@@ -3272,10 +3222,10 @@
         <v>1</v>
       </c>
       <c r="E77">
-        <v>0.56666666666666665</v>
+        <v>0.6</v>
       </c>
       <c r="F77">
-        <v>0.70833333333333337</v>
+        <v>0.75</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -3284,13 +3234,13 @@
         <v>1</v>
       </c>
       <c r="I77">
-        <v>0.80952380952380942</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J77">
-        <v>0.70833333333333337</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
       <c r="A78">
         <v>76</v>
       </c>
@@ -3304,25 +3254,25 @@
         <v>1</v>
       </c>
       <c r="E78">
-        <v>0.5</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="F78">
-        <v>0.625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H78">
         <v>1</v>
       </c>
       <c r="I78">
-        <v>0.66666666666666663</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="J78">
         <v>0.5</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10">
       <c r="A79">
         <v>77</v>
       </c>
@@ -3330,16 +3280,16 @@
         <v>87</v>
       </c>
       <c r="C79">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D79">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E79">
-        <v>0.6</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F79">
-        <v>0.75</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -3348,13 +3298,13 @@
         <v>1</v>
       </c>
       <c r="I79">
-        <v>0.5714285714285714</v>
+        <v>0.625</v>
       </c>
       <c r="J79">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
       <c r="A80">
         <v>78</v>
       </c>
@@ -3368,10 +3318,10 @@
         <v>1</v>
       </c>
       <c r="E80">
-        <v>0.53333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F80">
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -3380,13 +3330,13 @@
         <v>1</v>
       </c>
       <c r="I80">
-        <v>0.66666666666666663</v>
+        <v>0.5222222222222223</v>
       </c>
       <c r="J80">
         <v>0.5</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10">
       <c r="A81">
         <v>79</v>
       </c>
@@ -3400,10 +3350,10 @@
         <v>1</v>
       </c>
       <c r="E81">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F81">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -3412,13 +3362,13 @@
         <v>1</v>
       </c>
       <c r="I81">
-        <v>0.66666666666666663</v>
+        <v>0.5777777777777778</v>
       </c>
       <c r="J81">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.5833333333333334</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
       <c r="A82">
         <v>80</v>
       </c>
@@ -3426,31 +3376,31 @@
         <v>90</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E82">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F82">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="G82">
-        <v>0.5</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="H82">
         <v>0.5</v>
       </c>
       <c r="I82">
-        <v>1</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="J82">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.5833333333333334</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
       <c r="A83">
         <v>81</v>
       </c>
@@ -3458,7 +3408,7 @@
         <v>91</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3470,19 +3420,19 @@
         <v>0.75</v>
       </c>
       <c r="G83">
-        <v>0.5</v>
+        <v>0.3888888888888888</v>
       </c>
       <c r="H83">
         <v>1</v>
       </c>
       <c r="I83">
-        <v>0.65277777777777779</v>
+        <v>0.7714285714285714</v>
       </c>
       <c r="J83">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
       <c r="A84">
         <v>82</v>
       </c>
@@ -3490,7 +3440,7 @@
         <v>92</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3502,19 +3452,19 @@
         <v>0.75</v>
       </c>
       <c r="G84">
-        <v>0.5</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="H84">
         <v>1</v>
       </c>
       <c r="I84">
-        <v>0.74603174603174605</v>
+        <v>0.625</v>
       </c>
       <c r="J84">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
       <c r="A85">
         <v>83</v>
       </c>
@@ -3522,16 +3472,16 @@
         <v>93</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F85">
-        <v>0.75</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -3540,13 +3490,13 @@
         <v>1</v>
       </c>
       <c r="I85">
-        <v>0.54761904761904756</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J85">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
       <c r="A86">
         <v>84</v>
       </c>
@@ -3554,31 +3504,31 @@
         <v>94</v>
       </c>
       <c r="C86">
-        <v>0.77777777777777768</v>
+        <v>0.5</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E86">
-        <v>0.53333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F86">
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="G86">
-        <v>0.5</v>
+        <v>0.3888888888888888</v>
       </c>
       <c r="H86">
         <v>0.5</v>
       </c>
       <c r="I86">
-        <v>0.625</v>
+        <v>0.6777777777777777</v>
       </c>
       <c r="J86">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7916666666666666</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
       <c r="A87">
         <v>85</v>
       </c>
@@ -3592,10 +3542,10 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>0.56666666666666665</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F87">
-        <v>0.70833333333333337</v>
+        <v>0.875</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -3604,13 +3554,13 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>0.5714285714285714</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="J87">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
       <c r="A88">
         <v>86</v>
       </c>
@@ -3624,10 +3574,10 @@
         <v>1</v>
       </c>
       <c r="E88">
-        <v>0.5</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F88">
-        <v>0.625</v>
+        <v>0.875</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -3636,13 +3586,13 @@
         <v>1</v>
       </c>
       <c r="I88">
-        <v>0.5714285714285714</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="J88">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
       <c r="A89">
         <v>87</v>
       </c>
@@ -3650,31 +3600,31 @@
         <v>97</v>
       </c>
       <c r="C89">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D89">
         <v>1</v>
       </c>
       <c r="E89">
-        <v>0.6</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="F89">
-        <v>0.75</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="G89">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H89">
         <v>1</v>
       </c>
       <c r="I89">
-        <v>0.66666666666666663</v>
+        <v>0.462962962962963</v>
       </c>
       <c r="J89">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
       <c r="A90">
         <v>88</v>
       </c>
@@ -3688,10 +3638,10 @@
         <v>1</v>
       </c>
       <c r="E90">
-        <v>0.6333333333333333</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F90">
-        <v>0.79166666666666663</v>
+        <v>0.875</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -3700,13 +3650,13 @@
         <v>1</v>
       </c>
       <c r="I90">
-        <v>0.66666666666666663</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J90">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.5833333333333334</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
       <c r="A91">
         <v>89</v>
       </c>
@@ -3720,10 +3670,10 @@
         <v>1</v>
       </c>
       <c r="E91">
-        <v>0.53333333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F91">
-        <v>0.66666666666666663</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G91">
         <v>0.5</v>
@@ -3732,13 +3682,13 @@
         <v>1</v>
       </c>
       <c r="I91">
-        <v>0.60317460317460314</v>
+        <v>0.5648148148148148</v>
       </c>
       <c r="J91">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.5833333333333334</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
       <c r="A92">
         <v>90</v>
       </c>
@@ -3749,28 +3699,28 @@
         <v>1</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="E92">
-        <v>0.53333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="F92">
-        <v>0.66666666666666663</v>
+        <v>0.75</v>
       </c>
       <c r="G92">
         <v>1</v>
       </c>
       <c r="H92">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I92">
-        <v>0.68452380952380965</v>
+        <v>0.625</v>
       </c>
       <c r="J92">
         <v>0.625</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10">
       <c r="A93">
         <v>91</v>
       </c>
@@ -3790,19 +3740,19 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="G93">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H93">
         <v>1</v>
       </c>
       <c r="I93">
-        <v>0.75555555555555554</v>
+        <v>0.7238095238095239</v>
       </c>
       <c r="J93">
         <v>0.5714285714285714</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10">
       <c r="A94">
         <v>92</v>
       </c>
@@ -3810,31 +3760,31 @@
         <v>102</v>
       </c>
       <c r="C94">
-        <v>0.33333333333333331</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D94">
         <v>0.5</v>
       </c>
       <c r="E94">
-        <v>0.5</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="F94">
-        <v>0.625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G94">
-        <v>0.5</v>
+        <v>0.7777777777777777</v>
       </c>
       <c r="H94">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I94">
-        <v>0.61111111111111105</v>
+        <v>0.6444444444444444</v>
       </c>
       <c r="J94">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
       <c r="A95">
         <v>93</v>
       </c>
@@ -3842,31 +3792,31 @@
         <v>103</v>
       </c>
       <c r="C95">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D95">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E95">
-        <v>0.40000000000000008</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F95">
-        <v>0.5</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G95">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H95">
         <v>1</v>
       </c>
       <c r="I95">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J95">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7083333333333334</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
       <c r="A96">
         <v>94</v>
       </c>
@@ -3874,16 +3824,16 @@
         <v>104</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D96">
         <v>1</v>
       </c>
       <c r="E96">
-        <v>0.56666666666666665</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="F96">
-        <v>0.70833333333333337</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -3892,13 +3842,13 @@
         <v>1</v>
       </c>
       <c r="I96">
-        <v>0.72222222222222221</v>
+        <v>0.6583333333333333</v>
       </c>
       <c r="J96">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.7083333333333334</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10">
       <c r="A97">
         <v>95</v>
       </c>
@@ -3912,10 +3862,10 @@
         <v>0</v>
       </c>
       <c r="E97">
-        <v>0.40000000000000008</v>
+        <v>0.5</v>
       </c>
       <c r="F97">
-        <v>0.5714285714285714</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -3924,13 +3874,13 @@
         <v>0</v>
       </c>
       <c r="I97">
-        <v>0.80000000000000016</v>
+        <v>0.5423280423280423</v>
       </c>
       <c r="J97">
-        <v>0.5714285714285714</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.6190476190476191</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10">
       <c r="A98">
         <v>96</v>
       </c>
@@ -3938,31 +3888,31 @@
         <v>106</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D98">
         <v>1</v>
       </c>
       <c r="E98">
-        <v>0.5</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F98">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="G98">
+        <v>0.5555555555555555</v>
+      </c>
+      <c r="H98">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I98">
+        <v>0.5787037037037037</v>
+      </c>
+      <c r="J98">
         <v>0.625</v>
       </c>
-      <c r="G98">
-        <v>0.77777777777777768</v>
-      </c>
-      <c r="H98">
-        <v>1</v>
-      </c>
-      <c r="I98">
-        <v>0.68253968253968245</v>
-      </c>
-      <c r="J98">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:10">
       <c r="A99">
         <v>97</v>
       </c>
@@ -3976,10 +3926,10 @@
         <v>0</v>
       </c>
       <c r="E99">
-        <v>0.6</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="F99">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -3988,13 +3938,13 @@
         <v>0</v>
       </c>
       <c r="I99">
-        <v>0.52380952380952384</v>
+        <v>0.6</v>
       </c>
       <c r="J99">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10">
       <c r="A100">
         <v>98</v>
       </c>
@@ -4008,25 +3958,25 @@
         <v>1</v>
       </c>
       <c r="E100">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F100">
-        <v>0.7142857142857143</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="G100">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H100">
         <v>1</v>
       </c>
       <c r="I100">
-        <v>0.83333333333333337</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="J100">
-        <v>0.7142857142857143</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10">
       <c r="A101">
         <v>99</v>
       </c>
@@ -4043,7 +3993,7 @@
         <v>0.5</v>
       </c>
       <c r="F101">
-        <v>0.83333333333333337</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G101">
         <v>1</v>
@@ -4052,67 +4002,99 @@
         <v>1</v>
       </c>
       <c r="I101">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="J101">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C102">
-        <f>AVERAGE(C1:C101)</f>
-        <v>0.7072222222222222</v>
-      </c>
-      <c r="D102">
-        <f t="shared" ref="D102:J102" si="0">AVERAGE(D1:D101)</f>
-        <v>0.71499999999999997</v>
-      </c>
-      <c r="E102">
-        <f t="shared" si="0"/>
-        <v>0.53377777777777791</v>
-      </c>
-      <c r="F102">
-        <f t="shared" si="0"/>
-        <v>0.68373677248677223</v>
-      </c>
-      <c r="G102">
-        <f t="shared" si="0"/>
-        <v>0.72472222222222216</v>
-      </c>
-      <c r="H102">
-        <f t="shared" si="0"/>
-        <v>0.73083333333333345</v>
-      </c>
-      <c r="I102">
-        <f t="shared" si="0"/>
-        <v>0.69129761904761877</v>
-      </c>
-      <c r="J102">
-        <f t="shared" si="0"/>
-        <v>0.56027777777777765</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C2:F101">
-    <cfRule type="expression" dxfId="5" priority="1">
+  <conditionalFormatting sqref="C2:C101">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>C2&gt;G2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>C2&lt;G2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>C2=G2</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:J101">
-    <cfRule type="expression" dxfId="2" priority="4">
+  <conditionalFormatting sqref="D2:D101">
+    <cfRule type="expression" dxfId="0" priority="7">
+      <formula>D2&gt;H2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="8">
+      <formula>D2&lt;H2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="9">
+      <formula>D2=H2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E101">
+    <cfRule type="expression" dxfId="0" priority="13">
+      <formula>E2&gt;I2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="14">
+      <formula>E2&lt;I2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="15">
+      <formula>E2=I2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F101">
+    <cfRule type="expression" dxfId="0" priority="19">
+      <formula>F2&gt;J2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="20">
+      <formula>F2&lt;J2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="21">
+      <formula>F2=J2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G101">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>G2&gt;C2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="5">
       <formula>G2&lt;C2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="6">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>G2=C2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H101">
+    <cfRule type="expression" dxfId="0" priority="10">
+      <formula>H2&gt;D2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="11">
+      <formula>H2&lt;D2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="12">
+      <formula>H2=D2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I101">
+    <cfRule type="expression" dxfId="0" priority="16">
+      <formula>I2&gt;E2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="17">
+      <formula>I2&lt;E2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="18">
+      <formula>I2=E2</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J101">
+    <cfRule type="expression" dxfId="0" priority="22">
+      <formula>J2&gt;F2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="23">
+      <formula>J2&lt;F2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="24">
+      <formula>J2=F2</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4120,11 +4102,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>110</v>
       </c>
@@ -4144,84 +4126,84 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>116</v>
       </c>
       <c r="B2">
-        <v>0.70722222222222231</v>
+        <v>0.7672460317460319</v>
       </c>
       <c r="C2">
-        <v>0.72472222222222216</v>
+        <v>0.7461666666666668</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>117</v>
       </c>
       <c r="B3">
-        <v>0.71499999999999997</v>
+        <v>0.7883333333333333</v>
       </c>
       <c r="C3">
-        <v>0.73083333333333333</v>
+        <v>0.8080555555555555</v>
       </c>
       <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
         <v>12</v>
       </c>
-      <c r="E3">
-        <v>13</v>
-      </c>
       <c r="F3">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>118</v>
       </c>
       <c r="B4">
-        <v>0.53377777777777768</v>
+        <v>0.5969259259259259</v>
       </c>
       <c r="C4">
-        <v>0.69129761904761888</v>
+        <v>0.6686468253968253</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="F4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>119</v>
       </c>
       <c r="B5">
-        <v>0.68373677248677245</v>
+        <v>0.767063492063492</v>
       </c>
       <c r="C5">
-        <v>0.56027777777777765</v>
+        <v>0.7089021164021163</v>
       </c>
       <c r="D5">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -4230,11 +4212,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>110</v>
       </c>
@@ -4257,96 +4239,96 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>116</v>
       </c>
       <c r="B2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C2">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>117</v>
       </c>
       <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>78</v>
+      </c>
+      <c r="D3">
         <v>12</v>
       </c>
-      <c r="C3">
-        <v>75</v>
-      </c>
-      <c r="D3">
-        <v>13</v>
-      </c>
       <c r="E3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G3">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>118</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D4">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="E4">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>119</v>
       </c>
       <c r="B5">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="C5">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>72</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
